--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -36,10 +36,13 @@
     <t>m.hneef@student.aaup.edu</t>
   </si>
   <si>
-    <t>Mi@12345678</t>
+    <t>Mi@1234568</t>
   </si>
   <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
@@ -423,7 +426,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
